--- a/outputs/455-35.xlsx
+++ b/outputs/455-35.xlsx
@@ -128,12 +128,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -350,47 +354,47 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="29.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="29.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
